--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488232_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488232_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7569</v>
+        <v>0.9035</v>
       </c>
       <c r="E2" t="n">
-        <v>4.6973</v>
+        <v>4.8931</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.9403</v>
+        <v>-3.9896</v>
       </c>
       <c r="G2" t="n">
         <v>-0.4462</v>
@@ -610,13 +610,13 @@
         <v>2.4087</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.0563</v>
+        <v>-0.9096</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5508999999999999</v>
+        <v>-0.355</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5054</v>
+        <v>-0.5546</v>
       </c>
       <c r="V2" t="n">
         <v>1.8888</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3066</v>
+        <v>0.8208</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7398</v>
+        <v>1.2295</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4333</v>
+        <v>-0.4086</v>
       </c>
       <c r="G3" t="n">
         <v>0.3113</v>
@@ -688,13 +688,13 @@
         <v>0.9264</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7459</v>
+        <v>-0.2316</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6566</v>
+        <v>-0.1669</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0893</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1973</v>
+        <v>0.0031</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6137</v>
+        <v>2.1241</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.4164</v>
+        <v>-2.1209</v>
       </c>
       <c r="G4" t="n">
         <v>0.7664</v>
@@ -766,13 +766,13 @@
         <v>2.0382</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7543</v>
+        <v>-0.9485</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2114</v>
+        <v>-0.2782</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.9657</v>
+        <v>-0.6703</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1618</v>
+        <v>-0.2351</v>
       </c>
       <c r="E5" t="n">
-        <v>2.6567</v>
+        <v>2.5588</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.8185</v>
+        <v>-2.7939</v>
       </c>
       <c r="G5" t="n">
         <v>2.3397</v>
@@ -844,13 +844,13 @@
         <v>1.6676</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4089</v>
+        <v>-0.4822</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0584</v>
+        <v>-0.1564</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3504</v>
+        <v>-0.3258</v>
       </c>
       <c r="V5" t="n">
         <v>-2.8338</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. ELIAS GALLEGOS</t>
+          <t>C. ARANDA SUAREZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4556</v>
+        <v>-0.4873</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5218</v>
+        <v>2.366</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9774</v>
+        <v>-2.8533</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.5986</v>
+        <v>1.6956</v>
       </c>
       <c r="H6" t="n">
-        <v>0.025</v>
+        <v>2.594</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.6235</v>
+        <v>-0.8984</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.3112</v>
+        <v>4.0501</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8287</v>
+        <v>3.2207</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.1398</v>
+        <v>0.8294</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.2874</v>
+        <v>-2.3545</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8037</v>
+        <v>-0.6267</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4837</v>
+        <v>-1.7278</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1117</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1853</v>
+        <v>-1.8529</v>
       </c>
       <c r="R6" t="n">
-        <v>1.297</v>
+        <v>1.6676</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3457</v>
+        <v>-0.7393</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7039</v>
+        <v>-0.4607</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3581</v>
+        <v>-0.2786</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3144</v>
+        <v>-1.2583</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3144</v>
+        <v>0.6294</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6289</v>
+        <v>-1.8877</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. ARANDA SUAREZ</t>
+          <t>A. ELIAS GALLEGOS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4862</v>
+        <v>-0.6011</v>
       </c>
       <c r="E7" t="n">
-        <v>2.1701</v>
+        <v>0.1301</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.6563</v>
+        <v>-0.7312</v>
       </c>
       <c r="G7" t="n">
-        <v>1.6956</v>
+        <v>-1.5986</v>
       </c>
       <c r="H7" t="n">
-        <v>2.594</v>
+        <v>0.025</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8984</v>
+        <v>-1.6235</v>
       </c>
       <c r="J7" t="n">
-        <v>4.0501</v>
+        <v>-0.3112</v>
       </c>
       <c r="K7" t="n">
-        <v>3.2207</v>
+        <v>0.8287</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8294</v>
+        <v>-1.1398</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.3545</v>
+        <v>-1.2874</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6267</v>
+        <v>-0.8037</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.7278</v>
+        <v>-0.4837</v>
       </c>
       <c r="P7" t="n">
+        <v>1.1117</v>
+      </c>
+      <c r="Q7" t="n">
         <v>-0.1853</v>
       </c>
-      <c r="Q7" t="n">
-        <v>-1.8529</v>
-      </c>
       <c r="R7" t="n">
-        <v>1.6676</v>
+        <v>1.297</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7382</v>
+        <v>0.2002</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6566</v>
+        <v>0.3121</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.08160000000000001</v>
+        <v>-0.1119</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2583</v>
+        <v>-0.3144</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6294</v>
+        <v>0.3144</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.8877</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3185</v>
+        <v>-1.7606</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9076</v>
+        <v>-1.1034</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.411</v>
+        <v>-0.6572</v>
       </c>
       <c r="G8" t="n">
         <v>-3.7614</v>
@@ -1078,13 +1078,13 @@
         <v>1.8529</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7747000000000001</v>
+        <v>0.3326</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2114</v>
+        <v>0.0156</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5633</v>
+        <v>0.3171</v>
       </c>
       <c r="V8" t="n">
         <v>0.0005</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.6278</v>
+        <v>-2.555</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.719</v>
+        <v>-0.5232</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.9087</v>
+        <v>-2.0318</v>
       </c>
       <c r="G9" t="n">
         <v>-3.5269</v>
@@ -1156,13 +1156,13 @@
         <v>0.9264</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1579</v>
+        <v>0.2307</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0584</v>
+        <v>0.1374</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2164</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.7189</v>
+        <v>-3.5963</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5187</v>
+        <v>-1.4208</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.2001</v>
+        <v>-2.1755</v>
       </c>
       <c r="G10" t="n">
         <v>-0.7707000000000001</v>
@@ -1234,13 +1234,13 @@
         <v>0.1853</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3542</v>
+        <v>-0.2316</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1094</v>
+        <v>-0.0115</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2447</v>
+        <v>-0.2201</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1270,7 +1270,7 @@
         <v>-7.507999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>10.2541</v>
+        <v>10.2542</v>
       </c>
       <c r="F11" t="n">
         <v>-17.762</v>
@@ -1312,13 +1312,13 @@
         <v>12.9701</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.7795</v>
+        <v>-2.7793</v>
       </c>
       <c r="T11" t="n">
         <v>-0.9636</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.8155</v>
+        <v>-1.8156</v>
       </c>
       <c r="V11" t="n">
         <v>-2.5172</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>7.4605</v>
+        <v>8.366</v>
       </c>
       <c r="E12" t="n">
-        <v>9.866099999999999</v>
+        <v>10.8454</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.4056</v>
+        <v>-2.4795</v>
       </c>
       <c r="G12" t="n">
         <v>5.8184</v>
@@ -1390,13 +1390,13 @@
         <v>1.6676</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5044</v>
+        <v>0.401</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0396</v>
+        <v>-0.0603</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5352</v>
+        <v>0.4613</v>
       </c>
       <c r="V12" t="n">
         <v>2.5172</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.8389</v>
+        <v>6.0885</v>
       </c>
       <c r="E13" t="n">
-        <v>5.0063</v>
+        <v>6.0835</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1673</v>
+        <v>0.005</v>
       </c>
       <c r="G13" t="n">
         <v>1.6702</v>
@@ -1468,13 +1468,13 @@
         <v>1.8529</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7020999999999999</v>
+        <v>0.5475</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7113</v>
+        <v>0.3659</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0092</v>
+        <v>0.1815</v>
       </c>
       <c r="V13" t="n">
         <v>2.2033</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.2927</v>
+        <v>1.652</v>
       </c>
       <c r="E14" t="n">
-        <v>4.9677</v>
+        <v>3.4009</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.675</v>
+        <v>-1.7489</v>
       </c>
       <c r="G14" t="n">
         <v>3.8509</v>
@@ -1546,13 +1546,13 @@
         <v>2.0382</v>
       </c>
       <c r="S14" t="n">
-        <v>2.5535</v>
+        <v>0.9127999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2794</v>
+        <v>0.7126</v>
       </c>
       <c r="U14" t="n">
-        <v>0.274</v>
+        <v>0.2002</v>
       </c>
       <c r="V14" t="n">
         <v>-1.2589</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. LÓPEZ YUSTE</t>
+          <t>D. LARA CALDERA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3221</v>
+        <v>1.541</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3221</v>
+        <v>1.7543</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>-0.2132</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3221</v>
+        <v>-1.1625</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3221</v>
+        <v>-0.903</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>-0.2595</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3221</v>
+        <v>2.2477</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3221</v>
+        <v>2.0391</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>0.2086</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>-3.4102</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>-2.9421</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>-0.4681</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-2.0382</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.0382</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>0.1853</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>-0.0286</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>0.2139</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>2.5183</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.5733</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>0.945</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. MARTÍNEZ AGUDO</t>
+          <t>J. LÓPEZ YUSTE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. LARA CALDERA</t>
+          <t>A. MARTÍNEZ AGUDO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2674</v>
+        <v>0.3221</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5790999999999999</v>
+        <v>0.3221</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3117</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.1625</v>
+        <v>0.3221</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.903</v>
+        <v>0.3221</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2595</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>2.2477</v>
+        <v>0.3221</v>
       </c>
       <c r="K17" t="n">
-        <v>2.0391</v>
+        <v>0.3221</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2086</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.4102</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.9421</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4681</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.0382</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0382</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0883</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.2037</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1154</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>2.5183</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.5733</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.945</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.07140000000000001</v>
+        <v>-0.3209</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2465</v>
+        <v>-0.0473</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1751</v>
+        <v>-0.2736</v>
       </c>
       <c r="G18" t="n">
         <v>-0.8638</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6208</v>
+        <v>0.2285</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5434</v>
+        <v>0.2496</v>
       </c>
       <c r="U18" t="n">
-        <v>0.07729999999999999</v>
+        <v>-0.0211</v>
       </c>
       <c r="V18" t="n">
         <v>0.3144</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.3584</v>
+        <v>-2.0154</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.0607</v>
+        <v>-1.7669</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2977</v>
+        <v>-0.2485</v>
       </c>
       <c r="G19" t="n">
         <v>-2.1301</v>
@@ -1936,13 +1936,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7842</v>
+        <v>-0.4411</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7113</v>
+        <v>-0.4175</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.07290000000000001</v>
+        <v>-0.0236</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.616</v>
+        <v>-4.1096</v>
       </c>
       <c r="E20" t="n">
-        <v>1.3503</v>
+        <v>-0.1187</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.9663</v>
+        <v>-3.991</v>
       </c>
       <c r="G20" t="n">
         <v>0.4446</v>
@@ -2014,13 +2014,13 @@
         <v>1.6676</v>
       </c>
       <c r="S20" t="n">
-        <v>2.6075</v>
+        <v>1.1139</v>
       </c>
       <c r="T20" t="n">
-        <v>2.4436</v>
+        <v>0.9746</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1639</v>
+        <v>0.1393</v>
       </c>
       <c r="V20" t="n">
         <v>-2.5183</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.0928</v>
+        <v>-4.3379</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.8374</v>
+        <v>-3.0332</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2554</v>
+        <v>-1.3046</v>
       </c>
       <c r="G21" t="n">
         <v>-3.2811</v>
@@ -2092,13 +2092,13 @@
         <v>0.3706</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0766</v>
+        <v>-0.1685</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2151</v>
+        <v>0.0193</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1385</v>
+        <v>-0.1878</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2589</v>
@@ -2125,16 +2125,16 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>7.507899999999998</v>
+        <v>7.5079</v>
       </c>
       <c r="E22" t="n">
-        <v>17.7621</v>
+        <v>17.7622</v>
       </c>
       <c r="F22" t="n">
-        <v>-10.2541</v>
+        <v>-10.2543</v>
       </c>
       <c r="G22" t="n">
-        <v>4.9908</v>
+        <v>4.990799999999998</v>
       </c>
       <c r="H22" t="n">
         <v>-1.5379</v>
@@ -2176,7 +2176,7 @@
         <v>1.8156</v>
       </c>
       <c r="U22" t="n">
-        <v>0.9636</v>
+        <v>0.9637000000000002</v>
       </c>
       <c r="V22" t="n">
         <v>2.5171</v>
